--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.5389627698205</v>
+        <v>7.725081450095831</v>
       </c>
       <c r="D2" t="n">
-        <v>47.21600935585136</v>
+        <v>7.672601520325847</v>
       </c>
       <c r="E2" t="n">
-        <v>6.489697439307543</v>
+        <v>1.054575833887476</v>
       </c>
       <c r="F2" t="n">
-        <v>21.69726473831637</v>
+        <v>3.525805519976412</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.4066060703159</v>
+        <v>9.491073486426334</v>
       </c>
       <c r="D3" t="n">
-        <v>99.16247112851403</v>
+        <v>16.11390155838353</v>
       </c>
       <c r="E3" t="n">
-        <v>6.489697439307543</v>
+        <v>1.054575833887476</v>
       </c>
       <c r="F3" t="n">
-        <v>21.69726473831637</v>
+        <v>3.525805519976412</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.92571894492596</v>
+        <v>6.975429328550469</v>
       </c>
       <c r="D4" t="n">
-        <v>82.91778941647453</v>
+        <v>13.47414078017711</v>
       </c>
       <c r="E4" t="n">
-        <v>6.489697439307543</v>
+        <v>1.054575833887476</v>
       </c>
       <c r="F4" t="n">
-        <v>21.69726473831637</v>
+        <v>3.525805519976412</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
